--- a/practice/answers/q088.xlsx
+++ b/practice/answers/q088.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId3"/>
+    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,11 +47,22 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0024302A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0024302A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +74,18 @@
         <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,11 +93,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00A9C4AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9C4AE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9C4AE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9C4AE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9C4AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9C4AE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,7 +132,24 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8607,6 +8668,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004A7C59"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Question 38 — Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>(a)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Year on Rows, the two varieties on Columns and Yield shown as Average.</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>AAC Starbuck has the higher reported average in every year from 2020 through 2025.</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>The repeated pattern is more informative than one year, but it does not prove causation because growing locations and conditions may differ.</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>The live PivotTable (and chart, where requested) is on the PivotTable worksheet. The highlighted rows there show the values used in the written answers. The Data worksheet contains the source records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A9:D10"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -36347,13 +36508,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36362,158 +36523,151 @@
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Q88 — Year × Variety</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2"/>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Average of Yield_bu_ac</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Variety</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Average of Yield_bu_ac</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Variety</t>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AAC BRANDON (BW 932)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AAC STARBUCK &lt;SECAN&gt;</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>AAC BRANDON (BW 932)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>AAC STARBUCK &lt;SECAN&gt;</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>62.48936170212766</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>70.67999999999999</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>62.9030303030303</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>49.13666666666666</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>51.30597014925373</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>50.0624203821656</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>57.86896551724139</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>61.92162162162162</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>59.73167701863353</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>60.32023809523809</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>63.76973684210526</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>61.95874999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>62.32409638554216</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>66.24025974025975</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>64.20874999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>66.3358024691358</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>68.41199999999999</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>67.33397435897436</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>62.48936170212766</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>70.67999999999999</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>62.9030303030303</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>49.13666666666666</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>51.30597014925373</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>50.0624203821656</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>57.86896551724139</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>61.92162162162162</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>59.73167701863353</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>60.32023809523809</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>63.76973684210526</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>61.95874999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>62.32409638554216</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>66.24025974025975</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>64.20874999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>66.3358024691358</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>68.41199999999999</v>
+      <c r="B11" s="7" t="n">
+        <v>59.62215799614644</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>62.70320855614973</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>67.33397435897436</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>59.62215799614644</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>62.70320855614973</v>
-      </c>
-      <c r="D12" s="7" t="n">
         <v>60.91254199328107</v>
       </c>
     </row>
